--- a/tests/reports/vulnerability_test_report.xlsx
+++ b/tests/reports/vulnerability_test_report.xlsx
@@ -584,7 +584,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1251,7 @@
       </c>
       <c r="J2" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="J3" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -1359,7 +1359,7 @@
       </c>
       <c r="J4" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -1413,7 +1413,7 @@
       </c>
       <c r="J5" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1467,7 @@
       </c>
       <c r="J6" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -1521,7 +1521,7 @@
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="J8" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -1683,7 +1683,7 @@
       </c>
       <c r="J10" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -1737,7 +1737,7 @@
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -1791,7 +1791,7 @@
       </c>
       <c r="J12" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -1845,7 +1845,7 @@
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -1899,7 +1899,7 @@
       </c>
       <c r="J14" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -1953,7 +1953,7 @@
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -2007,7 +2007,7 @@
       </c>
       <c r="J16" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -2061,7 +2061,7 @@
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -2115,7 +2115,7 @@
       </c>
       <c r="J18" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="J20" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -2277,7 +2277,7 @@
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="J22" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -2385,7 +2385,7 @@
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="J24" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -2493,7 +2493,7 @@
       </c>
       <c r="J25" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -2547,7 +2547,7 @@
       </c>
       <c r="J26" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -2601,7 +2601,7 @@
       </c>
       <c r="J27" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -2655,7 +2655,7 @@
       </c>
       <c r="J28" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -2709,7 +2709,7 @@
       </c>
       <c r="J29" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -2763,7 +2763,7 @@
       </c>
       <c r="J30" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -2817,7 +2817,7 @@
       </c>
       <c r="J31" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -2871,7 +2871,7 @@
       </c>
       <c r="J32" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -2925,7 +2925,7 @@
       </c>
       <c r="J33" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -2979,7 +2979,7 @@
       </c>
       <c r="J34" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="J35" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -3087,7 +3087,7 @@
       </c>
       <c r="J36" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -3141,7 +3141,7 @@
       </c>
       <c r="J37" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -3195,7 +3195,7 @@
       </c>
       <c r="J38" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -3249,7 +3249,7 @@
       </c>
       <c r="J39" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -3303,7 +3303,7 @@
       </c>
       <c r="J40" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -3357,7 +3357,7 @@
       </c>
       <c r="J41" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -3411,7 +3411,7 @@
       </c>
       <c r="J42" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="J43" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -3519,7 +3519,7 @@
       </c>
       <c r="J44" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -3573,7 +3573,7 @@
       </c>
       <c r="J45" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -3627,7 +3627,7 @@
       </c>
       <c r="J46" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -3681,7 +3681,7 @@
       </c>
       <c r="J47" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -3735,7 +3735,7 @@
       </c>
       <c r="J48" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -3789,7 +3789,7 @@
       </c>
       <c r="J49" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -3843,7 +3843,7 @@
       </c>
       <c r="J50" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -3897,7 +3897,7 @@
       </c>
       <c r="J51" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -3950,7 +3950,7 @@
       </c>
       <c r="J52" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -4003,7 +4003,7 @@
       </c>
       <c r="J53" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -4056,7 +4056,7 @@
       </c>
       <c r="J54" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -4109,7 +4109,7 @@
       </c>
       <c r="J55" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -4162,7 +4162,7 @@
       </c>
       <c r="J56" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -4215,7 +4215,7 @@
       </c>
       <c r="J57" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -4268,7 +4268,7 @@
       </c>
       <c r="J58" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -4321,7 +4321,7 @@
       </c>
       <c r="J59" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="J60" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -4427,7 +4427,7 @@
       </c>
       <c r="J61" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -4480,7 +4480,7 @@
       </c>
       <c r="J62" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -4533,7 +4533,7 @@
       </c>
       <c r="J63" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -4586,7 +4586,7 @@
       </c>
       <c r="J64" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -4639,7 +4639,7 @@
       </c>
       <c r="J65" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="J66" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -4745,7 +4745,7 @@
       </c>
       <c r="J67" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -4798,7 +4798,7 @@
       </c>
       <c r="J68" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -4851,7 +4851,7 @@
       </c>
       <c r="J69" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="J70" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -4957,7 +4957,7 @@
       </c>
       <c r="J71" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -5010,7 +5010,7 @@
       </c>
       <c r="J72" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="J73" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -5116,7 +5116,7 @@
       </c>
       <c r="J74" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -5169,7 +5169,7 @@
       </c>
       <c r="J75" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -5222,7 +5222,7 @@
       </c>
       <c r="J76" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -5275,7 +5275,7 @@
       </c>
       <c r="J77" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -5328,7 +5328,7 @@
       </c>
       <c r="J78" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -5381,7 +5381,7 @@
       </c>
       <c r="J79" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -5434,7 +5434,7 @@
       </c>
       <c r="J80" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -5487,7 +5487,7 @@
       </c>
       <c r="J81" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="J82" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -5592,7 +5592,7 @@
       </c>
       <c r="J83" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -5644,7 +5644,7 @@
       </c>
       <c r="J84" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -5696,7 +5696,7 @@
       </c>
       <c r="J85" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -5748,7 +5748,7 @@
       </c>
       <c r="J86" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -5800,7 +5800,7 @@
       </c>
       <c r="J87" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -5852,7 +5852,7 @@
       </c>
       <c r="J88" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -5904,7 +5904,7 @@
       </c>
       <c r="J89" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -5956,7 +5956,7 @@
       </c>
       <c r="J90" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="J91" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -6060,7 +6060,7 @@
       </c>
       <c r="J92" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -6112,7 +6112,7 @@
       </c>
       <c r="J93" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -6164,7 +6164,7 @@
       </c>
       <c r="J94" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="J95" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -6268,7 +6268,7 @@
       </c>
       <c r="J96" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -6320,7 +6320,7 @@
       </c>
       <c r="J97" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -6372,7 +6372,7 @@
       </c>
       <c r="J98" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -6425,7 +6425,7 @@
       </c>
       <c r="J99" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -6477,7 +6477,7 @@
       </c>
       <c r="J100" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -6529,7 +6529,7 @@
       </c>
       <c r="J101" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -6582,7 +6582,7 @@
       </c>
       <c r="J102" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -6634,7 +6634,7 @@
       </c>
       <c r="J103" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="J104" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="J105" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -6790,7 +6790,7 @@
       </c>
       <c r="J106" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -6842,7 +6842,7 @@
       </c>
       <c r="J107" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="J108" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -6946,7 +6946,7 @@
       </c>
       <c r="J109" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -6998,7 +6998,7 @@
       </c>
       <c r="J110" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -7050,7 +7050,7 @@
       </c>
       <c r="J111" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -7102,7 +7102,7 @@
       </c>
       <c r="J112" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -7154,7 +7154,7 @@
       </c>
       <c r="J113" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -7206,7 +7206,7 @@
       </c>
       <c r="J114" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -7258,7 +7258,7 @@
       </c>
       <c r="J115" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -7310,7 +7310,7 @@
       </c>
       <c r="J116" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="J117" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -7415,7 +7415,7 @@
       </c>
       <c r="J118" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -7467,7 +7467,7 @@
       </c>
       <c r="J119" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -7519,7 +7519,7 @@
       </c>
       <c r="J120" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -7571,7 +7571,7 @@
       </c>
       <c r="J121" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -7624,7 +7624,7 @@
       </c>
       <c r="J122" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -7677,7 +7677,7 @@
       </c>
       <c r="J123" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -7730,7 +7730,7 @@
       </c>
       <c r="J124" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -7783,7 +7783,7 @@
       </c>
       <c r="J125" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -7836,7 +7836,7 @@
       </c>
       <c r="J126" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -7889,7 +7889,7 @@
       </c>
       <c r="J127" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -7942,7 +7942,7 @@
       </c>
       <c r="J128" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -7995,7 +7995,7 @@
       </c>
       <c r="J129" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -8048,7 +8048,7 @@
       </c>
       <c r="J130" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -8101,7 +8101,7 @@
       </c>
       <c r="J131" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="J132" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -8207,7 +8207,7 @@
       </c>
       <c r="J133" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -8260,7 +8260,7 @@
       </c>
       <c r="J134" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -8313,7 +8313,7 @@
       </c>
       <c r="J135" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -8366,7 +8366,7 @@
       </c>
       <c r="J136" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -8419,7 +8419,7 @@
       </c>
       <c r="J137" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -8472,7 +8472,7 @@
       </c>
       <c r="J138" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -8525,7 +8525,7 @@
       </c>
       <c r="J139" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -8578,7 +8578,7 @@
       </c>
       <c r="J140" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="J141" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -8684,7 +8684,7 @@
       </c>
       <c r="J142" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -8737,7 +8737,7 @@
       </c>
       <c r="J143" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -8790,7 +8790,7 @@
       </c>
       <c r="J144" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -8843,7 +8843,7 @@
       </c>
       <c r="J145" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="J146" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -8949,7 +8949,7 @@
       </c>
       <c r="J147" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -9002,7 +9002,7 @@
       </c>
       <c r="J148" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -9055,7 +9055,7 @@
       </c>
       <c r="J149" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -9108,7 +9108,7 @@
       </c>
       <c r="J150" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -9161,7 +9161,7 @@
       </c>
       <c r="J151" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -9214,7 +9214,7 @@
       </c>
       <c r="J152" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -9267,7 +9267,7 @@
       </c>
       <c r="J153" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -9320,7 +9320,7 @@
       </c>
       <c r="J154" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -9373,7 +9373,7 @@
       </c>
       <c r="J155" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -9426,7 +9426,7 @@
       </c>
       <c r="J156" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -9479,7 +9479,7 @@
       </c>
       <c r="J157" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -9532,7 +9532,7 @@
       </c>
       <c r="J158" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -9585,7 +9585,7 @@
       </c>
       <c r="J159" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -9638,7 +9638,7 @@
       </c>
       <c r="J160" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -9691,7 +9691,7 @@
       </c>
       <c r="J161" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -9744,7 +9744,7 @@
       </c>
       <c r="J162" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -9797,7 +9797,7 @@
       </c>
       <c r="J163" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -9850,7 +9850,7 @@
       </c>
       <c r="J164" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -9903,7 +9903,7 @@
       </c>
       <c r="J165" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -9956,7 +9956,7 @@
       </c>
       <c r="J166" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -10009,7 +10009,7 @@
       </c>
       <c r="J167" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -10062,7 +10062,7 @@
       </c>
       <c r="J168" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -10115,7 +10115,7 @@
       </c>
       <c r="J169" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -10168,7 +10168,7 @@
       </c>
       <c r="J170" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -10221,7 +10221,7 @@
       </c>
       <c r="J171" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -10274,7 +10274,7 @@
       </c>
       <c r="J172" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -10327,7 +10327,7 @@
       </c>
       <c r="J173" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -10380,7 +10380,7 @@
       </c>
       <c r="J174" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -10433,7 +10433,7 @@
       </c>
       <c r="J175" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -10486,7 +10486,7 @@
       </c>
       <c r="J176" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -10539,7 +10539,7 @@
       </c>
       <c r="J177" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -10592,7 +10592,7 @@
       </c>
       <c r="J178" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -10645,7 +10645,7 @@
       </c>
       <c r="J179" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -10698,7 +10698,7 @@
       </c>
       <c r="J180" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -10751,7 +10751,7 @@
       </c>
       <c r="J181" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -10804,7 +10804,7 @@
       </c>
       <c r="J182" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -10857,7 +10857,7 @@
       </c>
       <c r="J183" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -10910,7 +10910,7 @@
       </c>
       <c r="J184" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -10963,7 +10963,7 @@
       </c>
       <c r="J185" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -11016,7 +11016,7 @@
       </c>
       <c r="J186" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -11069,7 +11069,7 @@
       </c>
       <c r="J187" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -11122,7 +11122,7 @@
       </c>
       <c r="J188" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -11175,7 +11175,7 @@
       </c>
       <c r="J189" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -11228,7 +11228,7 @@
       </c>
       <c r="J190" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -11281,7 +11281,7 @@
       </c>
       <c r="J191" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -11334,7 +11334,7 @@
       </c>
       <c r="J192" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -11387,7 +11387,7 @@
       </c>
       <c r="J193" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -11440,7 +11440,7 @@
       </c>
       <c r="J194" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -11493,7 +11493,7 @@
       </c>
       <c r="J195" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -11546,7 +11546,7 @@
       </c>
       <c r="J196" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -11599,7 +11599,7 @@
       </c>
       <c r="J197" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -11652,7 +11652,7 @@
       </c>
       <c r="J198" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -11705,7 +11705,7 @@
       </c>
       <c r="J199" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -11758,7 +11758,7 @@
       </c>
       <c r="J200" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -11811,7 +11811,7 @@
       </c>
       <c r="J201" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -11864,7 +11864,7 @@
       </c>
       <c r="J202" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -11917,7 +11917,7 @@
       </c>
       <c r="J203" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -11970,7 +11970,7 @@
       </c>
       <c r="J204" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -12023,7 +12023,7 @@
       </c>
       <c r="J205" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -12076,7 +12076,7 @@
       </c>
       <c r="J206" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -12129,7 +12129,7 @@
       </c>
       <c r="J207" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -12182,7 +12182,7 @@
       </c>
       <c r="J208" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -12235,7 +12235,7 @@
       </c>
       <c r="J209" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -12288,7 +12288,7 @@
       </c>
       <c r="J210" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -12341,7 +12341,7 @@
       </c>
       <c r="J211" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -12394,7 +12394,7 @@
       </c>
       <c r="J212" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -12447,7 +12447,7 @@
       </c>
       <c r="J213" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -12500,7 +12500,7 @@
       </c>
       <c r="J214" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -12553,7 +12553,7 @@
       </c>
       <c r="J215" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -12606,7 +12606,7 @@
       </c>
       <c r="J216" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -12659,7 +12659,7 @@
       </c>
       <c r="J217" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -12712,7 +12712,7 @@
       </c>
       <c r="J218" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -12765,7 +12765,7 @@
       </c>
       <c r="J219" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -12818,7 +12818,7 @@
       </c>
       <c r="J220" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -12871,7 +12871,7 @@
       </c>
       <c r="J221" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -12924,7 +12924,7 @@
       </c>
       <c r="J222" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -12977,7 +12977,7 @@
       </c>
       <c r="J223" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -13030,7 +13030,7 @@
       </c>
       <c r="J224" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -13083,7 +13083,7 @@
       </c>
       <c r="J225" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -13136,7 +13136,7 @@
       </c>
       <c r="J226" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -13189,7 +13189,7 @@
       </c>
       <c r="J227" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -13242,7 +13242,7 @@
       </c>
       <c r="J228" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -13295,7 +13295,7 @@
       </c>
       <c r="J229" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -13348,7 +13348,7 @@
       </c>
       <c r="J230" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -13401,7 +13401,7 @@
       </c>
       <c r="J231" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -13454,7 +13454,7 @@
       </c>
       <c r="J232" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -13507,7 +13507,7 @@
       </c>
       <c r="J233" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -13560,7 +13560,7 @@
       </c>
       <c r="J234" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -13613,7 +13613,7 @@
       </c>
       <c r="J235" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -13666,7 +13666,7 @@
       </c>
       <c r="J236" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -13719,7 +13719,7 @@
       </c>
       <c r="J237" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -13772,7 +13772,7 @@
       </c>
       <c r="J238" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -13825,7 +13825,7 @@
       </c>
       <c r="J239" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -13878,7 +13878,7 @@
       </c>
       <c r="J240" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -13931,7 +13931,7 @@
       </c>
       <c r="J241" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -13984,7 +13984,7 @@
       </c>
       <c r="J242" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -14037,7 +14037,7 @@
       </c>
       <c r="J243" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -14090,7 +14090,7 @@
       </c>
       <c r="J244" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -14143,7 +14143,7 @@
       </c>
       <c r="J245" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -14196,7 +14196,7 @@
       </c>
       <c r="J246" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -14249,7 +14249,7 @@
       </c>
       <c r="J247" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -14302,7 +14302,7 @@
       </c>
       <c r="J248" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -14355,7 +14355,7 @@
       </c>
       <c r="J249" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -14408,7 +14408,7 @@
       </c>
       <c r="J250" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -14461,7 +14461,7 @@
       </c>
       <c r="J251" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -14514,7 +14514,7 @@
       </c>
       <c r="J252" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -14567,7 +14567,7 @@
       </c>
       <c r="J253" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -14620,7 +14620,7 @@
       </c>
       <c r="J254" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -14673,7 +14673,7 @@
       </c>
       <c r="J255" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -14726,7 +14726,7 @@
       </c>
       <c r="J256" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -14779,7 +14779,7 @@
       </c>
       <c r="J257" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -14832,7 +14832,7 @@
       </c>
       <c r="J258" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -14885,7 +14885,7 @@
       </c>
       <c r="J259" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -14938,7 +14938,7 @@
       </c>
       <c r="J260" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -14991,7 +14991,7 @@
       </c>
       <c r="J261" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -15044,7 +15044,7 @@
       </c>
       <c r="J262" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -15097,7 +15097,7 @@
       </c>
       <c r="J263" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -15150,7 +15150,7 @@
       </c>
       <c r="J264" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -15203,7 +15203,7 @@
       </c>
       <c r="J265" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -15256,7 +15256,7 @@
       </c>
       <c r="J266" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -15309,7 +15309,7 @@
       </c>
       <c r="J267" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -15362,7 +15362,7 @@
       </c>
       <c r="J268" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -15415,7 +15415,7 @@
       </c>
       <c r="J269" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -15468,7 +15468,7 @@
       </c>
       <c r="J270" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -15521,7 +15521,7 @@
       </c>
       <c r="J271" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="J272" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -15627,7 +15627,7 @@
       </c>
       <c r="J273" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -15680,7 +15680,7 @@
       </c>
       <c r="J274" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -15733,7 +15733,7 @@
       </c>
       <c r="J275" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -15786,7 +15786,7 @@
       </c>
       <c r="J276" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -15839,7 +15839,7 @@
       </c>
       <c r="J277" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -15892,7 +15892,7 @@
       </c>
       <c r="J278" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -15945,7 +15945,7 @@
       </c>
       <c r="J279" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -15998,7 +15998,7 @@
       </c>
       <c r="J280" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -16051,7 +16051,7 @@
       </c>
       <c r="J281" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -16104,7 +16104,7 @@
       </c>
       <c r="J282" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -16157,7 +16157,7 @@
       </c>
       <c r="J283" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -16210,7 +16210,7 @@
       </c>
       <c r="J284" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -16263,7 +16263,7 @@
       </c>
       <c r="J285" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="J286" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -16369,7 +16369,7 @@
       </c>
       <c r="J287" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -16422,7 +16422,7 @@
       </c>
       <c r="J288" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -16475,7 +16475,7 @@
       </c>
       <c r="J289" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -16528,7 +16528,7 @@
       </c>
       <c r="J290" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -16581,7 +16581,7 @@
       </c>
       <c r="J291" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -16634,7 +16634,7 @@
       </c>
       <c r="J292" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -16687,7 +16687,7 @@
       </c>
       <c r="J293" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -16740,7 +16740,7 @@
       </c>
       <c r="J294" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -16793,7 +16793,7 @@
       </c>
       <c r="J295" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -16846,7 +16846,7 @@
       </c>
       <c r="J296" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -16899,7 +16899,7 @@
       </c>
       <c r="J297" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -16952,7 +16952,7 @@
       </c>
       <c r="J298" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -17005,7 +17005,7 @@
       </c>
       <c r="J299" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -17058,7 +17058,7 @@
       </c>
       <c r="J300" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>
@@ -17111,7 +17111,7 @@
       </c>
       <c r="J301" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:40</t>
+          <t>2026-07-23 20:08:53</t>
         </is>
       </c>
     </row>

--- a/tests/reports/vulnerability_test_report.xlsx
+++ b/tests/reports/vulnerability_test_report.xlsx
@@ -584,7 +584,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1251,7 @@
       </c>
       <c r="J2" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="J3" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -1359,7 +1359,7 @@
       </c>
       <c r="J4" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -1413,7 +1413,7 @@
       </c>
       <c r="J5" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1467,7 @@
       </c>
       <c r="J6" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -1521,7 +1521,7 @@
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="J8" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -1683,7 +1683,7 @@
       </c>
       <c r="J10" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -1737,7 +1737,7 @@
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -1791,7 +1791,7 @@
       </c>
       <c r="J12" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -1845,7 +1845,7 @@
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -1899,7 +1899,7 @@
       </c>
       <c r="J14" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -1953,7 +1953,7 @@
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -2007,7 +2007,7 @@
       </c>
       <c r="J16" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -2061,7 +2061,7 @@
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -2115,7 +2115,7 @@
       </c>
       <c r="J18" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="J20" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -2277,7 +2277,7 @@
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="J22" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -2385,7 +2385,7 @@
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="J24" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -2493,7 +2493,7 @@
       </c>
       <c r="J25" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -2547,7 +2547,7 @@
       </c>
       <c r="J26" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -2601,7 +2601,7 @@
       </c>
       <c r="J27" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -2655,7 +2655,7 @@
       </c>
       <c r="J28" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -2709,7 +2709,7 @@
       </c>
       <c r="J29" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -2763,7 +2763,7 @@
       </c>
       <c r="J30" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -2817,7 +2817,7 @@
       </c>
       <c r="J31" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -2871,7 +2871,7 @@
       </c>
       <c r="J32" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -2925,7 +2925,7 @@
       </c>
       <c r="J33" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -2979,7 +2979,7 @@
       </c>
       <c r="J34" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="J35" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -3087,7 +3087,7 @@
       </c>
       <c r="J36" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -3141,7 +3141,7 @@
       </c>
       <c r="J37" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -3195,7 +3195,7 @@
       </c>
       <c r="J38" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -3249,7 +3249,7 @@
       </c>
       <c r="J39" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -3303,7 +3303,7 @@
       </c>
       <c r="J40" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -3357,7 +3357,7 @@
       </c>
       <c r="J41" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -3411,7 +3411,7 @@
       </c>
       <c r="J42" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="J43" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -3519,7 +3519,7 @@
       </c>
       <c r="J44" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -3573,7 +3573,7 @@
       </c>
       <c r="J45" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -3627,7 +3627,7 @@
       </c>
       <c r="J46" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -3681,7 +3681,7 @@
       </c>
       <c r="J47" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -3735,7 +3735,7 @@
       </c>
       <c r="J48" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -3789,7 +3789,7 @@
       </c>
       <c r="J49" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -3843,7 +3843,7 @@
       </c>
       <c r="J50" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -3897,7 +3897,7 @@
       </c>
       <c r="J51" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -3950,7 +3950,7 @@
       </c>
       <c r="J52" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -4003,7 +4003,7 @@
       </c>
       <c r="J53" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -4056,7 +4056,7 @@
       </c>
       <c r="J54" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -4109,7 +4109,7 @@
       </c>
       <c r="J55" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -4162,7 +4162,7 @@
       </c>
       <c r="J56" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -4215,7 +4215,7 @@
       </c>
       <c r="J57" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -4268,7 +4268,7 @@
       </c>
       <c r="J58" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -4321,7 +4321,7 @@
       </c>
       <c r="J59" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="J60" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -4427,7 +4427,7 @@
       </c>
       <c r="J61" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -4480,7 +4480,7 @@
       </c>
       <c r="J62" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -4533,7 +4533,7 @@
       </c>
       <c r="J63" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -4586,7 +4586,7 @@
       </c>
       <c r="J64" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -4639,7 +4639,7 @@
       </c>
       <c r="J65" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="J66" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -4745,7 +4745,7 @@
       </c>
       <c r="J67" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -4798,7 +4798,7 @@
       </c>
       <c r="J68" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -4851,7 +4851,7 @@
       </c>
       <c r="J69" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="J70" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -4957,7 +4957,7 @@
       </c>
       <c r="J71" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -5010,7 +5010,7 @@
       </c>
       <c r="J72" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="J73" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -5116,7 +5116,7 @@
       </c>
       <c r="J74" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -5169,7 +5169,7 @@
       </c>
       <c r="J75" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -5222,7 +5222,7 @@
       </c>
       <c r="J76" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -5275,7 +5275,7 @@
       </c>
       <c r="J77" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -5328,7 +5328,7 @@
       </c>
       <c r="J78" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -5381,7 +5381,7 @@
       </c>
       <c r="J79" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -5434,7 +5434,7 @@
       </c>
       <c r="J80" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -5487,7 +5487,7 @@
       </c>
       <c r="J81" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="J82" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -5592,7 +5592,7 @@
       </c>
       <c r="J83" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -5644,7 +5644,7 @@
       </c>
       <c r="J84" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -5696,7 +5696,7 @@
       </c>
       <c r="J85" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -5748,7 +5748,7 @@
       </c>
       <c r="J86" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -5800,7 +5800,7 @@
       </c>
       <c r="J87" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -5852,7 +5852,7 @@
       </c>
       <c r="J88" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -5904,7 +5904,7 @@
       </c>
       <c r="J89" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -5956,7 +5956,7 @@
       </c>
       <c r="J90" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="J91" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -6060,7 +6060,7 @@
       </c>
       <c r="J92" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -6112,7 +6112,7 @@
       </c>
       <c r="J93" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -6164,7 +6164,7 @@
       </c>
       <c r="J94" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="J95" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -6268,7 +6268,7 @@
       </c>
       <c r="J96" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -6320,7 +6320,7 @@
       </c>
       <c r="J97" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -6372,7 +6372,7 @@
       </c>
       <c r="J98" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -6425,7 +6425,7 @@
       </c>
       <c r="J99" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -6477,7 +6477,7 @@
       </c>
       <c r="J100" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -6529,7 +6529,7 @@
       </c>
       <c r="J101" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -6582,7 +6582,7 @@
       </c>
       <c r="J102" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -6634,7 +6634,7 @@
       </c>
       <c r="J103" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="J104" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="J105" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -6790,7 +6790,7 @@
       </c>
       <c r="J106" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -6842,7 +6842,7 @@
       </c>
       <c r="J107" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="J108" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -6946,7 +6946,7 @@
       </c>
       <c r="J109" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -6998,7 +6998,7 @@
       </c>
       <c r="J110" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -7050,7 +7050,7 @@
       </c>
       <c r="J111" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -7102,7 +7102,7 @@
       </c>
       <c r="J112" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -7154,7 +7154,7 @@
       </c>
       <c r="J113" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -7206,7 +7206,7 @@
       </c>
       <c r="J114" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -7258,7 +7258,7 @@
       </c>
       <c r="J115" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -7310,7 +7310,7 @@
       </c>
       <c r="J116" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="J117" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -7415,7 +7415,7 @@
       </c>
       <c r="J118" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -7467,7 +7467,7 @@
       </c>
       <c r="J119" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -7519,7 +7519,7 @@
       </c>
       <c r="J120" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -7571,7 +7571,7 @@
       </c>
       <c r="J121" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -7624,7 +7624,7 @@
       </c>
       <c r="J122" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -7677,7 +7677,7 @@
       </c>
       <c r="J123" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -7730,7 +7730,7 @@
       </c>
       <c r="J124" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -7783,7 +7783,7 @@
       </c>
       <c r="J125" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -7836,7 +7836,7 @@
       </c>
       <c r="J126" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -7889,7 +7889,7 @@
       </c>
       <c r="J127" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -7942,7 +7942,7 @@
       </c>
       <c r="J128" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -7995,7 +7995,7 @@
       </c>
       <c r="J129" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -8048,7 +8048,7 @@
       </c>
       <c r="J130" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -8101,7 +8101,7 @@
       </c>
       <c r="J131" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="J132" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -8207,7 +8207,7 @@
       </c>
       <c r="J133" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -8260,7 +8260,7 @@
       </c>
       <c r="J134" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -8313,7 +8313,7 @@
       </c>
       <c r="J135" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -8366,7 +8366,7 @@
       </c>
       <c r="J136" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -8419,7 +8419,7 @@
       </c>
       <c r="J137" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -8472,7 +8472,7 @@
       </c>
       <c r="J138" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -8525,7 +8525,7 @@
       </c>
       <c r="J139" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -8578,7 +8578,7 @@
       </c>
       <c r="J140" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="J141" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -8684,7 +8684,7 @@
       </c>
       <c r="J142" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -8737,7 +8737,7 @@
       </c>
       <c r="J143" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -8790,7 +8790,7 @@
       </c>
       <c r="J144" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -8843,7 +8843,7 @@
       </c>
       <c r="J145" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="J146" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -8949,7 +8949,7 @@
       </c>
       <c r="J147" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -9002,7 +9002,7 @@
       </c>
       <c r="J148" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -9055,7 +9055,7 @@
       </c>
       <c r="J149" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -9108,7 +9108,7 @@
       </c>
       <c r="J150" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -9161,7 +9161,7 @@
       </c>
       <c r="J151" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -9214,7 +9214,7 @@
       </c>
       <c r="J152" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -9267,7 +9267,7 @@
       </c>
       <c r="J153" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -9320,7 +9320,7 @@
       </c>
       <c r="J154" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -9373,7 +9373,7 @@
       </c>
       <c r="J155" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -9426,7 +9426,7 @@
       </c>
       <c r="J156" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -9479,7 +9479,7 @@
       </c>
       <c r="J157" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -9532,7 +9532,7 @@
       </c>
       <c r="J158" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -9585,7 +9585,7 @@
       </c>
       <c r="J159" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -9638,7 +9638,7 @@
       </c>
       <c r="J160" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -9691,7 +9691,7 @@
       </c>
       <c r="J161" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -9744,7 +9744,7 @@
       </c>
       <c r="J162" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -9797,7 +9797,7 @@
       </c>
       <c r="J163" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -9850,7 +9850,7 @@
       </c>
       <c r="J164" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -9903,7 +9903,7 @@
       </c>
       <c r="J165" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -9956,7 +9956,7 @@
       </c>
       <c r="J166" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -10009,7 +10009,7 @@
       </c>
       <c r="J167" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -10062,7 +10062,7 @@
       </c>
       <c r="J168" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -10115,7 +10115,7 @@
       </c>
       <c r="J169" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -10168,7 +10168,7 @@
       </c>
       <c r="J170" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -10221,7 +10221,7 @@
       </c>
       <c r="J171" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -10274,7 +10274,7 @@
       </c>
       <c r="J172" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -10327,7 +10327,7 @@
       </c>
       <c r="J173" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -10380,7 +10380,7 @@
       </c>
       <c r="J174" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -10433,7 +10433,7 @@
       </c>
       <c r="J175" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -10486,7 +10486,7 @@
       </c>
       <c r="J176" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -10539,7 +10539,7 @@
       </c>
       <c r="J177" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -10592,7 +10592,7 @@
       </c>
       <c r="J178" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -10645,7 +10645,7 @@
       </c>
       <c r="J179" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -10698,7 +10698,7 @@
       </c>
       <c r="J180" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -10751,7 +10751,7 @@
       </c>
       <c r="J181" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -10804,7 +10804,7 @@
       </c>
       <c r="J182" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -10857,7 +10857,7 @@
       </c>
       <c r="J183" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -10910,7 +10910,7 @@
       </c>
       <c r="J184" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -10963,7 +10963,7 @@
       </c>
       <c r="J185" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -11016,7 +11016,7 @@
       </c>
       <c r="J186" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -11069,7 +11069,7 @@
       </c>
       <c r="J187" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -11122,7 +11122,7 @@
       </c>
       <c r="J188" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -11175,7 +11175,7 @@
       </c>
       <c r="J189" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -11228,7 +11228,7 @@
       </c>
       <c r="J190" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -11281,7 +11281,7 @@
       </c>
       <c r="J191" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -11334,7 +11334,7 @@
       </c>
       <c r="J192" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -11387,7 +11387,7 @@
       </c>
       <c r="J193" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -11440,7 +11440,7 @@
       </c>
       <c r="J194" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -11493,7 +11493,7 @@
       </c>
       <c r="J195" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -11546,7 +11546,7 @@
       </c>
       <c r="J196" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -11599,7 +11599,7 @@
       </c>
       <c r="J197" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -11652,7 +11652,7 @@
       </c>
       <c r="J198" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -11705,7 +11705,7 @@
       </c>
       <c r="J199" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -11758,7 +11758,7 @@
       </c>
       <c r="J200" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -11811,7 +11811,7 @@
       </c>
       <c r="J201" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -11864,7 +11864,7 @@
       </c>
       <c r="J202" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -11917,7 +11917,7 @@
       </c>
       <c r="J203" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -11970,7 +11970,7 @@
       </c>
       <c r="J204" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -12023,7 +12023,7 @@
       </c>
       <c r="J205" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -12076,7 +12076,7 @@
       </c>
       <c r="J206" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -12129,7 +12129,7 @@
       </c>
       <c r="J207" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -12182,7 +12182,7 @@
       </c>
       <c r="J208" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -12235,7 +12235,7 @@
       </c>
       <c r="J209" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -12288,7 +12288,7 @@
       </c>
       <c r="J210" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -12341,7 +12341,7 @@
       </c>
       <c r="J211" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -12394,7 +12394,7 @@
       </c>
       <c r="J212" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -12447,7 +12447,7 @@
       </c>
       <c r="J213" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -12500,7 +12500,7 @@
       </c>
       <c r="J214" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -12553,7 +12553,7 @@
       </c>
       <c r="J215" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -12606,7 +12606,7 @@
       </c>
       <c r="J216" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -12659,7 +12659,7 @@
       </c>
       <c r="J217" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -12712,7 +12712,7 @@
       </c>
       <c r="J218" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -12765,7 +12765,7 @@
       </c>
       <c r="J219" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -12818,7 +12818,7 @@
       </c>
       <c r="J220" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -12871,7 +12871,7 @@
       </c>
       <c r="J221" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -12924,7 +12924,7 @@
       </c>
       <c r="J222" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -12977,7 +12977,7 @@
       </c>
       <c r="J223" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -13030,7 +13030,7 @@
       </c>
       <c r="J224" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -13083,7 +13083,7 @@
       </c>
       <c r="J225" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -13136,7 +13136,7 @@
       </c>
       <c r="J226" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -13189,7 +13189,7 @@
       </c>
       <c r="J227" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -13242,7 +13242,7 @@
       </c>
       <c r="J228" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -13295,7 +13295,7 @@
       </c>
       <c r="J229" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -13348,7 +13348,7 @@
       </c>
       <c r="J230" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -13401,7 +13401,7 @@
       </c>
       <c r="J231" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -13454,7 +13454,7 @@
       </c>
       <c r="J232" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -13507,7 +13507,7 @@
       </c>
       <c r="J233" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -13560,7 +13560,7 @@
       </c>
       <c r="J234" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -13613,7 +13613,7 @@
       </c>
       <c r="J235" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -13666,7 +13666,7 @@
       </c>
       <c r="J236" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -13719,7 +13719,7 @@
       </c>
       <c r="J237" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -13772,7 +13772,7 @@
       </c>
       <c r="J238" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -13825,7 +13825,7 @@
       </c>
       <c r="J239" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -13878,7 +13878,7 @@
       </c>
       <c r="J240" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -13931,7 +13931,7 @@
       </c>
       <c r="J241" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -13984,7 +13984,7 @@
       </c>
       <c r="J242" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -14037,7 +14037,7 @@
       </c>
       <c r="J243" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -14090,7 +14090,7 @@
       </c>
       <c r="J244" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -14143,7 +14143,7 @@
       </c>
       <c r="J245" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -14196,7 +14196,7 @@
       </c>
       <c r="J246" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -14249,7 +14249,7 @@
       </c>
       <c r="J247" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -14302,7 +14302,7 @@
       </c>
       <c r="J248" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -14355,7 +14355,7 @@
       </c>
       <c r="J249" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -14408,7 +14408,7 @@
       </c>
       <c r="J250" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -14461,7 +14461,7 @@
       </c>
       <c r="J251" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -14514,7 +14514,7 @@
       </c>
       <c r="J252" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -14567,7 +14567,7 @@
       </c>
       <c r="J253" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -14620,7 +14620,7 @@
       </c>
       <c r="J254" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -14673,7 +14673,7 @@
       </c>
       <c r="J255" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -14726,7 +14726,7 @@
       </c>
       <c r="J256" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -14779,7 +14779,7 @@
       </c>
       <c r="J257" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -14832,7 +14832,7 @@
       </c>
       <c r="J258" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -14885,7 +14885,7 @@
       </c>
       <c r="J259" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -14938,7 +14938,7 @@
       </c>
       <c r="J260" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -14991,7 +14991,7 @@
       </c>
       <c r="J261" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -15044,7 +15044,7 @@
       </c>
       <c r="J262" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -15097,7 +15097,7 @@
       </c>
       <c r="J263" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -15150,7 +15150,7 @@
       </c>
       <c r="J264" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -15203,7 +15203,7 @@
       </c>
       <c r="J265" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -15256,7 +15256,7 @@
       </c>
       <c r="J266" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -15309,7 +15309,7 @@
       </c>
       <c r="J267" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -15362,7 +15362,7 @@
       </c>
       <c r="J268" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -15415,7 +15415,7 @@
       </c>
       <c r="J269" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -15468,7 +15468,7 @@
       </c>
       <c r="J270" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -15521,7 +15521,7 @@
       </c>
       <c r="J271" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="J272" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -15627,7 +15627,7 @@
       </c>
       <c r="J273" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -15680,7 +15680,7 @@
       </c>
       <c r="J274" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -15733,7 +15733,7 @@
       </c>
       <c r="J275" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -15786,7 +15786,7 @@
       </c>
       <c r="J276" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -15839,7 +15839,7 @@
       </c>
       <c r="J277" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -15892,7 +15892,7 @@
       </c>
       <c r="J278" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -15945,7 +15945,7 @@
       </c>
       <c r="J279" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -15998,7 +15998,7 @@
       </c>
       <c r="J280" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -16051,7 +16051,7 @@
       </c>
       <c r="J281" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -16104,7 +16104,7 @@
       </c>
       <c r="J282" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -16157,7 +16157,7 @@
       </c>
       <c r="J283" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -16210,7 +16210,7 @@
       </c>
       <c r="J284" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -16263,7 +16263,7 @@
       </c>
       <c r="J285" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="J286" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -16369,7 +16369,7 @@
       </c>
       <c r="J287" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -16422,7 +16422,7 @@
       </c>
       <c r="J288" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -16475,7 +16475,7 @@
       </c>
       <c r="J289" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -16528,7 +16528,7 @@
       </c>
       <c r="J290" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -16581,7 +16581,7 @@
       </c>
       <c r="J291" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -16634,7 +16634,7 @@
       </c>
       <c r="J292" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -16687,7 +16687,7 @@
       </c>
       <c r="J293" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -16740,7 +16740,7 @@
       </c>
       <c r="J294" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -16793,7 +16793,7 @@
       </c>
       <c r="J295" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -16846,7 +16846,7 @@
       </c>
       <c r="J296" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -16899,7 +16899,7 @@
       </c>
       <c r="J297" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -16952,7 +16952,7 @@
       </c>
       <c r="J298" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -17005,7 +17005,7 @@
       </c>
       <c r="J299" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -17058,7 +17058,7 @@
       </c>
       <c r="J300" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
@@ -17111,7 +17111,7 @@
       </c>
       <c r="J301" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:53</t>
+          <t>2026-07-24 08:35:00</t>
         </is>
       </c>
     </row>
